--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA80444A-6FAF-488F-A8A9-24EDED26CA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2556" yWindow="4548" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,13 +24,96 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>zh</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>！搞定</t>
+  </si>
+  <si>
+    <t>刚刚在墙角拿了块扁石头，正好能卡在铁门的门轴下面</t>
+  </si>
+  <si>
+    <t>真不敢想象要是一阵风刮过来，把这铁门给合上了，后果得多麻烦</t>
+  </si>
+  <si>
+    <t>这种老式的门锁要是出个意外，从天台内侧是绝对打不开的</t>
+  </si>
+  <si>
+    <t>要是真被困在上面……总不能指望有人恰好上来救我吧</t>
+  </si>
+  <si>
+    <t>这地方，除了保洁阿姨固定来打扫，或者外校人来参观的时候，平时根本没人</t>
+  </si>
+  <si>
+    <t>done!</t>
+  </si>
+  <si>
+    <t>I just picked up a flat stone in the corner; it fits perfectly under the hinge of the iron door.</t>
+  </si>
+  <si>
+    <t>I can’t even imagine if a gust of wind came and slammed this iron door shut—what a mess that would be.</t>
+  </si>
+  <si>
+    <t>If something goes wrong with this old-style lock, there’s absolutely no way to open it from the rooftop side.</t>
+  </si>
+  <si>
+    <t>If I really got trapped up here... I can’t count on someone happening to come up and rescue me.</t>
+  </si>
+  <si>
+    <t>Aside from the cleaning lady coming on a fixed schedule, or when people from other schools come to visit, there’s basically no one here.</t>
+  </si>
+  <si>
+    <t>……总算到六楼了，教学楼的顶层</t>
+  </si>
+  <si>
+    <t>从教室一路逃过来，腿都软了……早知道平时应该多锻炼的</t>
+  </si>
+  <si>
+    <t>楼层的布局倒是很简单，一到四楼是上课的教室，五楼是老师们的办公室，行政主任室也在那一层……</t>
+  </si>
+  <si>
+    <t>刚才在五楼差点撞上教务主任，真够倒霉的</t>
+  </si>
+  <si>
+    <t>上次来……是上周？还是上上周？具体时间完全想不起来了</t>
+  </si>
+  <si>
+    <t>不过费了这么大劲才上来，反正来都来了，先四处逛逛吧</t>
+  </si>
+  <si>
+    <t>...finally made it to the sixth floor, the top of the academic building.</t>
+  </si>
+  <si>
+    <t>I ran all the way here from the classroom; my legs are jelly... I should’ve exercised more.</t>
+  </si>
+  <si>
+    <t>The layout is pretty simple: floors one through four are classrooms, the fifth floor is the teachers’ offices, and the administrative director’s office is on that floor too...</t>
+  </si>
+  <si>
+    <t>I almost ran into the academic dean on the fifth floor just now—what rotten luck.</t>
+  </si>
+  <si>
+    <t>The last time I came... was it last week? Or the week before? I can’t remember exactly.</t>
+  </si>
+  <si>
+    <t>But since it took so much effort to get up here—well, I’m here anyway—let’s look around a bit first.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -53,7 +142,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +419,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="66.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA80444A-6FAF-488F-A8A9-24EDED26CA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63EBE18-5072-4FC1-AE56-02D247F40A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2556" yWindow="4548" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6780" yWindow="1704" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>zh</t>
   </si>
@@ -103,6 +103,126 @@
   </si>
   <si>
     <t>But since it took so much effort to get up here—well, I’m here anyway—let’s look around a bit first.</t>
+  </si>
+  <si>
+    <t>现在你可以按下WASD和方向键来移动人物</t>
+  </si>
+  <si>
+    <t>在移动的过程中按下右Shift键可以快速移动</t>
+  </si>
+  <si>
+    <t>顺着地上的脚印移动到身后的告示牌上吧</t>
+  </si>
+  <si>
+    <t>You can now move the character with WASD and the arrow keys.</t>
+  </si>
+  <si>
+    <t>While moving, press Right Shift to move faster.</t>
+  </si>
+  <si>
+    <t>Follow the footprints on the ground to the notice board behind you.</t>
+  </si>
+  <si>
+    <t>靠近可交互的物体时，人物上方将显示交互图标</t>
+  </si>
+  <si>
+    <t>同时系统会高亮该物体，使其呈现黄色外发光</t>
+  </si>
+  <si>
+    <t>[!] 表示重要物品，请务必探索，它影响着剧情的推动</t>
+  </si>
+  <si>
+    <t>[眼睛] 表示普通物体，是否探索并不影响关键剧情</t>
+  </si>
+  <si>
+    <t>[√] 表示已完成探索</t>
+  </si>
+  <si>
+    <t>每当交互图标出现，你可以&lt;color=#FFC600&gt;按下对话键&lt;/color&gt;或&lt;color=#FFC600&gt;点击鼠标&lt;/color&gt;执行交互操作</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFC600&gt;面前的告示牌&lt;/color&gt;似乎写着什么，请试着与其交互看看</t>
+  </si>
+  <si>
+    <t>When you approach an interactive object, an interaction icon will appear above the character.</t>
+  </si>
+  <si>
+    <t>At the same time, the system will highlight that object with a yellow outer glow.</t>
+  </si>
+  <si>
+    <t>[!] indicates an important item—be sure to investigate it, as it affects story progression.</t>
+  </si>
+  <si>
+    <t>[Eye] indicates a regular object; investigating it does not affect the main story.</t>
+  </si>
+  <si>
+    <t>[√] indicates that exploration is complete.</t>
+  </si>
+  <si>
+    <t>Whenever the interaction icon appears, you can &lt;color=#FFC600&gt;press the Talk key&lt;/color&gt; or &lt;color=#FFC600&gt;click the mouse&lt;/color&gt; to interact.</t>
+  </si>
+  <si>
+    <t>The &lt;color=#FFC600&gt;notice board in front of you&lt;/color&gt; seems to have something written on it—try interacting with it.</t>
+  </si>
+  <si>
+    <t>看来你已经熟悉了如何与场景中的物品互动</t>
+  </si>
+  <si>
+    <t>现在是时候去确认一下系统菜单了，它提供了许多有用的功能：</t>
+  </si>
+  <si>
+    <t>[设置] 你可以根据个人喜好，随时调整游戏的按键、画面和声音效果</t>
+  </si>
+  <si>
+    <t>[背包] 用于查看、使用或整理你收集到的所有任务物品和资源</t>
+  </si>
+  <si>
+    <t>[日记] 提供实时任务提示，当你不确定下一步该做什么时，请随时查阅</t>
+  </si>
+  <si>
+    <t>现在请尝试按下ESC键，打开系统的主菜单吧</t>
+  </si>
+  <si>
+    <t>Looks like you’re already familiar with interacting with objects in the scene.</t>
+  </si>
+  <si>
+    <t>Now it’s time to check the system menu; it offers many useful functions:</t>
+  </si>
+  <si>
+    <t>[Settings] Adjust controls, graphics, and audio to your preference at any time.</t>
+  </si>
+  <si>
+    <t>[Inventory] View, use, or organize all the quest items and resources you’ve collected.</t>
+  </si>
+  <si>
+    <t>[Journal] Provides real-time quest hints; check it whenever you’re unsure what to do next.</t>
+  </si>
+  <si>
+    <t>Now try pressing ESC to open the main system menu.</t>
+  </si>
+  <si>
+    <t>一个保洁用的拖把，上面留有没干透的水痕，旁边放着半瓶除草剂</t>
+  </si>
+  <si>
+    <t>拖把还是湿的，看来保洁阿姨早上刚清理过</t>
+  </si>
+  <si>
+    <t>就算有学校保洁定期清理，天台上还是长满了青苔</t>
+  </si>
+  <si>
+    <t>这些东西太顽固了，用刷子使劲刷都未必能刷下一层</t>
+  </si>
+  <si>
+    <t>A janitorial mop with not-yet-dry water streaks; beside it sits a half-full bottle of herbicide.</t>
+  </si>
+  <si>
+    <t>The mop is still wet—looks like the custodian just cleaned this morning.</t>
+  </si>
+  <si>
+    <t>Even with regular school cleanups, the rooftop is still covered in moss.</t>
+  </si>
+  <si>
+    <t>It’s so stubborn that even a hard scrub with a brush might not remove a layer.</t>
   </si>
 </sst>
 </file>
@@ -420,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="66.88671875" customWidth="1"/>
@@ -531,6 +651,166 @@
         <v>25</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63EBE18-5072-4FC1-AE56-02D247F40A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FBDFE2-376F-436B-89F6-8A9E2E007166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="1704" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5388" yWindow="4092" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>zh</t>
   </si>
@@ -84,27 +84,6 @@
     <t>上次来……是上周？还是上上周？具体时间完全想不起来了</t>
   </si>
   <si>
-    <t>不过费了这么大劲才上来，反正来都来了，先四处逛逛吧</t>
-  </si>
-  <si>
-    <t>...finally made it to the sixth floor, the top of the academic building.</t>
-  </si>
-  <si>
-    <t>I ran all the way here from the classroom; my legs are jelly... I should’ve exercised more.</t>
-  </si>
-  <si>
-    <t>The layout is pretty simple: floors one through four are classrooms, the fifth floor is the teachers’ offices, and the administrative director’s office is on that floor too...</t>
-  </si>
-  <si>
-    <t>I almost ran into the academic dean on the fifth floor just now—what rotten luck.</t>
-  </si>
-  <si>
-    <t>The last time I came... was it last week? Or the week before? I can’t remember exactly.</t>
-  </si>
-  <si>
-    <t>But since it took so much effort to get up here—well, I’m here anyway—let’s look around a bit first.</t>
-  </si>
-  <si>
     <t>现在你可以按下WASD和方向键来移动人物</t>
   </si>
   <si>
@@ -223,6 +202,45 @@
   </si>
   <si>
     <t>It’s so stubborn that even a hard scrub with a brush might not remove a layer.</t>
+  </si>
+  <si>
+    <t>说起来，这地方我好像也不是第一次来了……</t>
+  </si>
+  <si>
+    <t>费了这么大劲才上来，要是什么都不干就下去,也不知道能去哪里</t>
+  </si>
+  <si>
+    <t>……教室是肯定回不去了，我可不想在众目睽睽之下被老师堵在门口训话</t>
+  </si>
+  <si>
+    <t>既然来都来了，先四处逛逛吧</t>
+  </si>
+  <si>
+    <t>...Finally made it to the sixth floor—the top of the academic building.</t>
+  </si>
+  <si>
+    <t>I ran all the way from the classroom; my legs are jelly... I really should work out more.</t>
+  </si>
+  <si>
+    <t>The layout is pretty simple: floors one through four are classrooms; the fifth floor is the teachers’ offices, and the administrative director’s office is there too...</t>
+  </si>
+  <si>
+    <t>I almost ran into the academic affairs director on the fifth floor just now—just my luck.</t>
+  </si>
+  <si>
+    <t>Come to think of it, this doesn’t seem like my first time here...</t>
+  </si>
+  <si>
+    <t>Last time... was it last week? Or the week before? I can’t remember the exact time at all.</t>
+  </si>
+  <si>
+    <t>After all that effort to get up here, if I go back down without doing anything, I don’t even know where I could go.</t>
+  </si>
+  <si>
+    <t>...Going back to the classroom is definitely not happening; I don’t want to get stopped at the door and lectured in front of everyone.</t>
+  </si>
+  <si>
+    <t>Since I’m already here, I might as well take a look around first.</t>
   </si>
 </sst>
 </file>
@@ -540,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="66.88671875" customWidth="1"/>
@@ -608,7 +626,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -616,7 +634,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -624,7 +642,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -632,183 +650,207 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FBDFE2-376F-436B-89F6-8A9E2E007166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB87E5F-12B4-4491-BE2A-86D731B8D81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5388" yWindow="4092" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4368" yWindow="3816" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>zh</t>
   </si>
@@ -241,6 +241,102 @@
   </si>
   <si>
     <t>Since I’m already here, I might as well take a look around first.</t>
+  </si>
+  <si>
+    <t>&lt;任务开启&gt;</t>
+  </si>
+  <si>
+    <t>&lt;MISSION START&gt;</t>
+  </si>
+  <si>
+    <t>一堆随处可见的碎石头</t>
+  </si>
+  <si>
+    <t>石块的缝隙间生长着一些鲜黄色的花朵，与右侧花圃中种植的品种相同</t>
+  </si>
+  <si>
+    <t>看来是风把花圃的种子带到了这里</t>
+  </si>
+  <si>
+    <t>这些花开得倒是挺倔强</t>
+  </si>
+  <si>
+    <t>（你注意到一抹银光在花影间闪烁）</t>
+  </si>
+  <si>
+    <t>连石头缝里都藏着惊喜呢……</t>
+  </si>
+  <si>
+    <t>你将&lt;color=#FFC600&gt; [一枚硬币] &lt;/color&gt;放入了背包</t>
+  </si>
+  <si>
+    <t>A scatter of loose stones lies everywhere.</t>
+  </si>
+  <si>
+    <t>Bright yellow flowers grow in the gaps between the stones, the same variety as those planted in the flowerbed to the right.</t>
+  </si>
+  <si>
+    <t>It seems the wind carried seeds from the flowerbed over here.</t>
+  </si>
+  <si>
+    <t>These flowers are blooming with stubborn tenacity.</t>
+  </si>
+  <si>
+    <t>(You notice a flash of silver glint among the flowers’ shadows.)</t>
+  </si>
+  <si>
+    <t>Even the cracks between the stones hide surprises...</t>
+  </si>
+  <si>
+    <t>You put &lt;color=#FFC600&gt;[a coin]&lt;/color&gt; into your bag.</t>
+  </si>
+  <si>
+    <t>一台指示灯亮起的自助售货机</t>
+  </si>
+  <si>
+    <t>机内饮品陈列整齐，价格标签清晰</t>
+  </si>
+  <si>
+    <t>有意思，这种地方居然有台正常供电的售货机</t>
+  </si>
+  <si>
+    <t>正好我有点口渴了</t>
+  </si>
+  <si>
+    <t>（你饶有兴致地浏览着商品，直到看见价格）</t>
+  </si>
+  <si>
+    <t>哇，最便宜的矿泉水都要三枚硬币啊……</t>
+  </si>
+  <si>
+    <t>（你不甘心地翻遍所有口袋，最终无力地垂下头）</t>
+  </si>
+  <si>
+    <t>……这种时候，要是能像动漫里一样，踢一下售货机就能掉出一瓶该多好</t>
+  </si>
+  <si>
+    <t>A vending machine with its indicator light on.</t>
+  </si>
+  <si>
+    <t>Inside, the drinks are neatly arranged and the price tags are clear.</t>
+  </si>
+  <si>
+    <t>Huh, interesting—there’s actually a vending machine here that still has power.</t>
+  </si>
+  <si>
+    <t>Perfect, I’m a little thirsty.</t>
+  </si>
+  <si>
+    <t>(You browse the items with interest—until you see the prices.)</t>
+  </si>
+  <si>
+    <t>Wow, even the cheapest bottled water costs three coins...</t>
+  </si>
+  <si>
+    <t>(You rummage through every pocket in frustration, then let your head drop.)</t>
+  </si>
+  <si>
+    <t>...If only it worked like in anime—one good kick and a bottle would pop out.</t>
   </si>
 </sst>
 </file>
@@ -558,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="66.88671875" customWidth="1"/>
@@ -853,6 +949,134 @@
         <v>58</v>
       </c>
     </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>95</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB87E5F-12B4-4491-BE2A-86D731B8D81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBE619A-6B9F-45DF-8F8F-53BC777EF0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4368" yWindow="3816" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2784" yWindow="2664" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t>zh</t>
   </si>
@@ -312,9 +312,6 @@
     <t>（你不甘心地翻遍所有口袋，最终无力地垂下头）</t>
   </si>
   <si>
-    <t>……这种时候，要是能像动漫里一样，踢一下售货机就能掉出一瓶该多好</t>
-  </si>
-  <si>
     <t>A vending machine with its indicator light on.</t>
   </si>
   <si>
@@ -336,7 +333,124 @@
     <t>(You rummage through every pocket in frustration, then let your head drop.)</t>
   </si>
   <si>
-    <t>...If only it worked like in anime—one good kick and a bottle would pop out.</t>
+    <t>一片自然形成的草甸，各种不知名的草肆意生长在一起</t>
+  </si>
+  <si>
+    <t>它们自在生长的样子，莫名让人觉得亲切</t>
+  </si>
+  <si>
+    <t>（你正准备离开，手无意间伸进口袋，指尖触到那几枚刚从天台角落捡来的硬币）</t>
+  </si>
+  <si>
+    <t>太好了！刚才捡的硬币刚好派上用场！</t>
+  </si>
+  <si>
+    <t>（暂时还不太想喝）</t>
+  </si>
+  <si>
+    <t>……主要是这价格，还是再考虑考虑吧</t>
+  </si>
+  <si>
+    <t>（你迫不及待地将三枚硬币塞入投币口，按下按钮）</t>
+  </si>
+  <si>
+    <t>冰凉的液体滑过喉咙，那股灼热的焦躁感终于被镇压了下去</t>
+  </si>
+  <si>
+    <t>我靠着售货机，长长地舒了一口气</t>
+  </si>
+  <si>
+    <t>世界仿佛在这一刻被按下了静音键，只剩下心跳逐渐平复的节奏</t>
+  </si>
+  <si>
+    <t>真是不可思议……就是这么普通的东西</t>
+  </si>
+  <si>
+    <t>却让我感受到一种被世界宽恕的安宁</t>
+  </si>
+  <si>
+    <t>像有人把体内那根紧绷的弦轻轻松开</t>
+  </si>
+  <si>
+    <t>我把空瓶在掌心转了半圈，指尖还残着冰意</t>
+  </si>
+  <si>
+    <t>售货机的嗡鸣退到远处，光线落在地面，慢慢把影子抚平</t>
+  </si>
+  <si>
+    <t>（你的硬币数量不够）</t>
+  </si>
+  <si>
+    <t>……看来想喝到水，得先在天台上凑够三枚硬币才行</t>
+  </si>
+  <si>
+    <t>总觉得……刚才好像错过了什么地方，再回去确认一下吧</t>
+  </si>
+  <si>
+    <t>一个繁茂的花圃，以鲜黄色花朵为主</t>
+  </si>
+  <si>
+    <t>看来只能去&lt;color=#FFC600&gt;天台边缘&lt;/color&gt;和&lt;color=#FFC600&gt;角落&lt;/color&gt;仔细找找了，说不定那里能发现什么</t>
+  </si>
+  <si>
+    <t>Looks like I’ll have to search the &lt;color=#FFC600&gt;rooftop edge&lt;/color&gt; and the &lt;color=#FFC600&gt;corners&lt;/color&gt; carefully—maybe there’s something there.</t>
+  </si>
+  <si>
+    <t>(Just as you’re about to leave, your hand slips into your pocket; your fingertips touch the coins you picked up from the rooftop corner.)</t>
+  </si>
+  <si>
+    <t>Perfect! The coins I found earlier are just what I need!</t>
+  </si>
+  <si>
+    <t>(I don’t really feel like drinking right now.)</t>
+  </si>
+  <si>
+    <t>…Mostly because of the price—maybe I should think twice.</t>
+  </si>
+  <si>
+    <t>(Impatiently, you feed three coins into the slot and press the button.)</t>
+  </si>
+  <si>
+    <t>The chilled liquid slides down my throat, and that burning restlessness is finally subdued.</t>
+  </si>
+  <si>
+    <t>I lean against the vending machine and let out a long breath.</t>
+  </si>
+  <si>
+    <t>For a moment, the world seems to hit mute; only the slowing rhythm of my heartbeat remains.</t>
+  </si>
+  <si>
+    <t>Incredible… something so ordinary,</t>
+  </si>
+  <si>
+    <t>yet it fills me with a calm, as if the world has forgiven me.</t>
+  </si>
+  <si>
+    <t>Like someone gently loosening a taut string inside me.</t>
+  </si>
+  <si>
+    <t>I twirl the empty bottle half a turn in my palm; a trace of cold still lingers on my fingertips.</t>
+  </si>
+  <si>
+    <t>The vending machine’s hum recedes into the distance; light falls across the ground, slowly smoothing the shadows.</t>
+  </si>
+  <si>
+    <t>(You don’t have enough coins.)</t>
+  </si>
+  <si>
+    <t>…Looks like I’ll need to gather three coins on the rooftop if I want a drink.</t>
+  </si>
+  <si>
+    <t>I can’t shake the feeling I missed something—better go back and check.</t>
+  </si>
+  <si>
+    <t>A naturally formed meadow where all kinds of nameless grasses grow wild together.</t>
+  </si>
+  <si>
+    <t>The way they grow freely gives off a strangely familiar warmth.</t>
+  </si>
+  <si>
+    <t>A lush flowerbed, dominated by bright yellow blossoms.</t>
   </si>
 </sst>
 </file>
@@ -654,10 +768,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="66.88671875" customWidth="1"/>
+    <col min="1" max="1" width="64.44140625" customWidth="1"/>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1018,7 +1132,7 @@
         <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1026,7 +1140,7 @@
         <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -1034,7 +1148,7 @@
         <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1042,7 +1156,7 @@
         <v>91</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1050,7 +1164,7 @@
         <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1058,7 +1172,7 @@
         <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1066,15 +1180,167 @@
         <v>94</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>112</v>
+      </c>
+      <c r="B61" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B62" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>116</v>
+      </c>
+      <c r="B65" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>117</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>118</v>
+      </c>
+      <c r="B67" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>119</v>
+      </c>
+      <c r="B68" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>103</v>
+      </c>
+      <c r="B70" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBE619A-6B9F-45DF-8F8F-53BC777EF0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC78BC51-EF37-4EA8-B848-98D6768584A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2784" yWindow="2664" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5064" yWindow="2736" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t>zh</t>
   </si>
@@ -336,9 +336,6 @@
     <t>一片自然形成的草甸，各种不知名的草肆意生长在一起</t>
   </si>
   <si>
-    <t>它们自在生长的样子，莫名让人觉得亲切</t>
-  </si>
-  <si>
     <t>（你正准备离开，手无意间伸进口袋，指尖触到那几枚刚从天台角落捡来的硬币）</t>
   </si>
   <si>
@@ -444,13 +441,130 @@
     <t>I can’t shake the feeling I missed something—better go back and check.</t>
   </si>
   <si>
-    <t>A naturally formed meadow where all kinds of nameless grasses grow wild together.</t>
-  </si>
-  <si>
-    <t>The way they grow freely gives off a strangely familiar warmth.</t>
-  </si>
-  <si>
-    <t>A lush flowerbed, dominated by bright yellow blossoms.</t>
+    <t>一个边角有些磨坏但看起来十分结实的铁制公告栏，靠近有消毒水的气味</t>
+  </si>
+  <si>
+    <t>上面的字迹被淡淡的青苔遮住，但依旧可以辨认：</t>
+  </si>
+  <si>
+    <t>为保安全，请勿倚靠或攀爬防护栏</t>
+  </si>
+  <si>
+    <t>看上去无人打理的长椅，椅脚以及周围的地面都长出了青苔</t>
+  </si>
+  <si>
+    <t>一个保洁用的拖把，上面留有没有干透的水痕，旁边放着半瓶除草剂</t>
+  </si>
+  <si>
+    <t>除草剂的瓶身冰凉，瓶口散发着一股格外刺鼻的化学药剂味</t>
+  </si>
+  <si>
+    <t>从这湿拖把就能看出来，保洁阿姨早上指定是来打扫过了</t>
+  </si>
+  <si>
+    <t>可这空气里，霉味跟一股刺鼻的药水味混在一块儿，也太难顶了</t>
+  </si>
+  <si>
+    <t>阿姨这是下了猛料啊，杀毒效果先不说，杀伤力是够强的</t>
+  </si>
+  <si>
+    <t>一扇紧闭的老旧铁门，门锁看上去十分牢固</t>
+  </si>
+  <si>
+    <t>随处可见的碎石头</t>
+  </si>
+  <si>
+    <t>碎石下有微光闪烁</t>
+  </si>
+  <si>
+    <t>你伸手拨开碎石，经过翻找，从泥土中拾起了一枚银色的硬币</t>
+  </si>
+  <si>
+    <t>你再次翻找了这些碎石，但没有任何新的发现</t>
+  </si>
+  <si>
+    <t>什么都没有发现</t>
+  </si>
+  <si>
+    <t>果然，天上不会掉两次馅饼</t>
+  </si>
+  <si>
+    <t>空气里混杂着消毒水的化学气味、湿拖把散发的霉旧气息，以及泥土本身的味道</t>
+  </si>
+  <si>
+    <t>细看之下，不少植株都呈现不自然的萎蔫状态</t>
+  </si>
+  <si>
+    <t>这是什么生态灾难现场吗</t>
+  </si>
+  <si>
+    <t>说是草甸，结果土壤里全是化学药剂的味道和霉味</t>
+  </si>
+  <si>
+    <t>A bench that appears untended, with moss growing on its legs and on the surrounding ground</t>
+  </si>
+  <si>
+    <t>A tightly shut old iron door; the lock looks very secure</t>
+  </si>
+  <si>
+    <t>A lush flowerbed dominated by bright yellow blossoms</t>
+  </si>
+  <si>
+    <t>An iron bulletin board with worn corners but looking very sturdy; up close there’s a smell of disinfectant</t>
+  </si>
+  <si>
+    <t>The writing on it is veiled by a light moss, but still legible:</t>
+  </si>
+  <si>
+    <t>For safety, please do not lean on or climb the guardrail</t>
+  </si>
+  <si>
+    <t>A cleaning mop with still-damp streaks on it, and next to it a half-full bottle of herbicide</t>
+  </si>
+  <si>
+    <t>The herbicide’s bottle is cold to the touch, and the mouth gives off an especially acrid chemical odor</t>
+  </si>
+  <si>
+    <t>From this wet mop you can tell the cleaning lady definitely came by to clean this morning</t>
+  </si>
+  <si>
+    <t>But in the air, the mustiness mixed with a sharp medicinal reek is just unbearable</t>
+  </si>
+  <si>
+    <t>She really went heavy on the stuff—never mind the disinfecting effect, the potency is plenty</t>
+  </si>
+  <si>
+    <t>Bits of gravel everywhere</t>
+  </si>
+  <si>
+    <t>A faint glimmer flickers beneath the gravel</t>
+  </si>
+  <si>
+    <t>You reach out to clear the gravel and, after searching, pick up a silver coin from the soil</t>
+  </si>
+  <si>
+    <t>You search through the gravel again, but find nothing new</t>
+  </si>
+  <si>
+    <t>You find nothing</t>
+  </si>
+  <si>
+    <t>As expected, pies don’t fall from the sky twice</t>
+  </si>
+  <si>
+    <t>A naturally formed meadow, with all kinds of unknown grasses growing unchecked together</t>
+  </si>
+  <si>
+    <t>The air is a mix of the chemical smell of disinfectant, the musty staleness from the wet mop, and the scent of the earth itself</t>
+  </si>
+  <si>
+    <t>On closer look, many plants show an unnatural wilted state</t>
+  </si>
+  <si>
+    <t>Is this some kind of ecological disaster scene?</t>
+  </si>
+  <si>
+    <t>Call it a meadow, yet the soil reeks of chemicals and mildew</t>
   </si>
 </sst>
 </file>
@@ -768,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="64.44140625" customWidth="1"/>
@@ -1185,162 +1299,314 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" t="s">
         <v>121</v>
-      </c>
-      <c r="B52" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>138</v>
+      </c>
+      <c r="B72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>142</v>
+      </c>
+      <c r="B75" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>145</v>
+      </c>
+      <c r="B78" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>146</v>
+      </c>
+      <c r="B79" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>149</v>
+      </c>
+      <c r="B81" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>151</v>
+      </c>
+      <c r="B83" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>152</v>
+      </c>
+      <c r="B84" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>153</v>
+      </c>
+      <c r="B85" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>156</v>
+      </c>
+      <c r="B89" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>157</v>
+      </c>
+      <c r="B90" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC78BC51-EF37-4EA8-B848-98D6768584A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CDFAD3-A0F9-4671-BC0F-BAE84622F49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5064" yWindow="2736" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3456" yWindow="4836" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <si>
     <t>zh</t>
   </si>
@@ -144,66 +144,6 @@
     <t>The &lt;color=#FFC600&gt;notice board in front of you&lt;/color&gt; seems to have something written on it—try interacting with it.</t>
   </si>
   <si>
-    <t>看来你已经熟悉了如何与场景中的物品互动</t>
-  </si>
-  <si>
-    <t>现在是时候去确认一下系统菜单了，它提供了许多有用的功能：</t>
-  </si>
-  <si>
-    <t>[设置] 你可以根据个人喜好，随时调整游戏的按键、画面和声音效果</t>
-  </si>
-  <si>
-    <t>[背包] 用于查看、使用或整理你收集到的所有任务物品和资源</t>
-  </si>
-  <si>
-    <t>[日记] 提供实时任务提示，当你不确定下一步该做什么时，请随时查阅</t>
-  </si>
-  <si>
-    <t>现在请尝试按下ESC键，打开系统的主菜单吧</t>
-  </si>
-  <si>
-    <t>Looks like you’re already familiar with interacting with objects in the scene.</t>
-  </si>
-  <si>
-    <t>Now it’s time to check the system menu; it offers many useful functions:</t>
-  </si>
-  <si>
-    <t>[Settings] Adjust controls, graphics, and audio to your preference at any time.</t>
-  </si>
-  <si>
-    <t>[Inventory] View, use, or organize all the quest items and resources you’ve collected.</t>
-  </si>
-  <si>
-    <t>[Journal] Provides real-time quest hints; check it whenever you’re unsure what to do next.</t>
-  </si>
-  <si>
-    <t>Now try pressing ESC to open the main system menu.</t>
-  </si>
-  <si>
-    <t>一个保洁用的拖把，上面留有没干透的水痕，旁边放着半瓶除草剂</t>
-  </si>
-  <si>
-    <t>拖把还是湿的，看来保洁阿姨早上刚清理过</t>
-  </si>
-  <si>
-    <t>就算有学校保洁定期清理，天台上还是长满了青苔</t>
-  </si>
-  <si>
-    <t>这些东西太顽固了，用刷子使劲刷都未必能刷下一层</t>
-  </si>
-  <si>
-    <t>A janitorial mop with not-yet-dry water streaks; beside it sits a half-full bottle of herbicide.</t>
-  </si>
-  <si>
-    <t>The mop is still wet—looks like the custodian just cleaned this morning.</t>
-  </si>
-  <si>
-    <t>Even with regular school cleanups, the rooftop is still covered in moss.</t>
-  </si>
-  <si>
-    <t>It’s so stubborn that even a hard scrub with a brush might not remove a layer.</t>
-  </si>
-  <si>
     <t>说起来，这地方我好像也不是第一次来了……</t>
   </si>
   <si>
@@ -222,12 +162,6 @@
     <t>I ran all the way from the classroom; my legs are jelly... I really should work out more.</t>
   </si>
   <si>
-    <t>The layout is pretty simple: floors one through four are classrooms; the fifth floor is the teachers’ offices, and the administrative director’s office is there too...</t>
-  </si>
-  <si>
-    <t>I almost ran into the academic affairs director on the fifth floor just now—just my luck.</t>
-  </si>
-  <si>
     <t>Come to think of it, this doesn’t seem like my first time here...</t>
   </si>
   <si>
@@ -510,9 +444,6 @@
     <t>A lush flowerbed dominated by bright yellow blossoms</t>
   </si>
   <si>
-    <t>An iron bulletin board with worn corners but looking very sturdy; up close there’s a smell of disinfectant</t>
-  </si>
-  <si>
     <t>The writing on it is veiled by a light moss, but still legible:</t>
   </si>
   <si>
@@ -522,15 +453,9 @@
     <t>A cleaning mop with still-damp streaks on it, and next to it a half-full bottle of herbicide</t>
   </si>
   <si>
-    <t>The herbicide’s bottle is cold to the touch, and the mouth gives off an especially acrid chemical odor</t>
-  </si>
-  <si>
     <t>From this wet mop you can tell the cleaning lady definitely came by to clean this morning</t>
   </si>
   <si>
-    <t>But in the air, the mustiness mixed with a sharp medicinal reek is just unbearable</t>
-  </si>
-  <si>
     <t>She really went heavy on the stuff—never mind the disinfecting effect, the potency is plenty</t>
   </si>
   <si>
@@ -549,9 +474,6 @@
     <t>You find nothing</t>
   </si>
   <si>
-    <t>As expected, pies don’t fall from the sky twice</t>
-  </si>
-  <si>
     <t>A naturally formed meadow, with all kinds of unknown grasses growing unchecked together</t>
   </si>
   <si>
@@ -565,6 +487,252 @@
   </si>
   <si>
     <t>Call it a meadow, yet the soil reeks of chemicals and mildew</t>
+  </si>
+  <si>
+    <t>哇？这个告示牌……</t>
+  </si>
+  <si>
+    <t>上面青苔少得厉害，还留着些被硬生生蹭掉的痕迹……</t>
+  </si>
+  <si>
+    <t>虽然可能是我多心了，但这种糟糕的感觉真让人不舒服</t>
+  </si>
+  <si>
+    <t>真希望这是我的错觉……</t>
+  </si>
+  <si>
+    <t>既然上来了，还是把在意的地方都好好看看吧</t>
+  </si>
+  <si>
+    <t>告示牌是检查完了……接下来该检查哪里来着？</t>
+  </si>
+  <si>
+    <t>在游戏中，你需要通过完成&lt;color=#FFC600&gt;日记&lt;/color&gt;中的事项来推进剧情</t>
+  </si>
+  <si>
+    <t>在日记界面中，你可以通过条目的&lt;color=#FFC600&gt;颜色&lt;/color&gt;辨别任务状态：</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFC600&gt;灰色&lt;/color&gt;代表未完成</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFC600&gt;白色&lt;/color&gt;代表已完成</t>
+  </si>
+  <si>
+    <t>当你清空当前日记中的所有&lt;color=#FFC600&gt;灰色&lt;/color&gt;条目时，会触发关键剧情</t>
+  </si>
+  <si>
+    <t>现在请按下&lt;color=#FFC600&gt;ESC&lt;/color&gt;键，打开系统的主菜单查阅日记</t>
+  </si>
+  <si>
+    <t>接下来，好好探索天台吧！</t>
+  </si>
+  <si>
+    <t>需要留意的地方应该记在日记里面了</t>
+  </si>
+  <si>
+    <t>我记得日记里提到了几个关键点：左边的草甸、右边的盆栽，以及保洁工具和除草剂的组合</t>
+  </si>
+  <si>
+    <t>重点看看这些地方吧，说不定就能搞清楚心中那种糟糕的感觉是什么了</t>
+  </si>
+  <si>
+    <t>终于凑齐三枚硬币了</t>
+  </si>
+  <si>
+    <t>现在去售货机那里看看吧</t>
+  </si>
+  <si>
+    <t>应该可以买矿泉水了</t>
+  </si>
+  <si>
+    <t>The moss on it is greatly reduced, and there are still marks where it was forcibly rubbed off...</t>
+  </si>
+  <si>
+    <t>Although I might be overthinking it, this awful feeling is really uncomfortable</t>
+  </si>
+  <si>
+    <t>I really hope this is just my imagination...</t>
+  </si>
+  <si>
+    <t>Since I’m up here, I should carefully check all the places I’m concerned about</t>
+  </si>
+  <si>
+    <t>The notice board is checked... what should I examine next again?</t>
+  </si>
+  <si>
+    <t>In the game, you need to advance the story by completing the items in the &lt;color=#FFC600&gt;Journal&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>In the journal interface, you can distinguish task status by the &lt;color=#FFC600&gt;color&lt;/color&gt; of the entries:</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFC600&gt;Gray&lt;/color&gt; represents not completed</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFC600&gt;White&lt;/color&gt; represents completed</t>
+  </si>
+  <si>
+    <t>When you clear all the &lt;color=#FFC600&gt;gray&lt;/color&gt; entries in the current journal, a key plot will be triggered</t>
+  </si>
+  <si>
+    <t>Now please press the &lt;color=#FFC600&gt;ESC&lt;/color&gt; key to open the system main menu and check the journal</t>
+  </si>
+  <si>
+    <t>Next, go explore the rooftop properly!</t>
+  </si>
+  <si>
+    <t>The places that need attention should be recorded in the journal</t>
+  </si>
+  <si>
+    <t>I remember the journal mentioned a few key points: the meadow on the left, the potted plants on the right, and the combination of cleaning tools and herbicide</t>
+  </si>
+  <si>
+    <t>Finally gathered three coins</t>
+  </si>
+  <si>
+    <t>Now go take a look at the vending machine</t>
+  </si>
+  <si>
+    <t>I should be able to buy mineral water now</t>
+  </si>
+  <si>
+    <t>Focus on these places; maybe I can figure out what that awful feeling inside is</t>
+  </si>
+  <si>
+    <t>一扇虚掩着的老旧铁门，门轴上卡着一块显眼的扁石头</t>
+  </si>
+  <si>
+    <t>刚刚放的石头还卡在门轴上……现在最好别去动它</t>
+  </si>
+  <si>
+    <t>万一碰掉了石头，导致这扇门关上……我就真出不去了</t>
+  </si>
+  <si>
+    <t>你瞥见下水道缝隙中隐隐透着银色的微光</t>
+  </si>
+  <si>
+    <t>但扑鼻的异味和黏腻的污垢让你立刻后退半步</t>
+  </si>
+  <si>
+    <t>这味道……可真够提神醒脑的</t>
+  </si>
+  <si>
+    <t>我可不想为这么点钱弄脏手</t>
+  </si>
+  <si>
+    <t>我的尊严，可比一枚硬币值钱多了</t>
+  </si>
+  <si>
+    <t>（你努力不让自己的目光停留在那里，快步离开）</t>
+  </si>
+  <si>
+    <t>让硬币留在这里污染环境，也是一种罪过吧？</t>
+  </si>
+  <si>
+    <t>对，我这是在……清理环境！</t>
+  </si>
+  <si>
+    <t>（你迅速蹲下了身，小心翼翼地用指甲抠出了硬币）</t>
+  </si>
+  <si>
+    <t>Whoa—this notice board…</t>
+  </si>
+  <si>
+    <t>But the mustiness mixed with a sharp chemical reek in the air is really hard to bear.</t>
+  </si>
+  <si>
+    <t>A nondescript storm drain; the area around it is slick with moisture.</t>
+  </si>
+  <si>
+    <t>You catch a faint silver gleam seeping through the drain’s gaps.</t>
+  </si>
+  <si>
+    <t>But the stench and the clammy grime make you instinctively step back.</t>
+  </si>
+  <si>
+    <t>This smell… sure is eye-opening.</t>
+  </si>
+  <si>
+    <t>I’m not getting my hands dirty for that little money.</t>
+  </si>
+  <si>
+    <t>My dignity is worth far more than a single coin.</t>
+  </si>
+  <si>
+    <t>(You force your eyes away and hurry off.)</t>
+  </si>
+  <si>
+    <t>Leaving a coin here to pollute the environment is a sin too, isn’t it?</t>
+  </si>
+  <si>
+    <t>(You crouch quickly and carefully pry the coin out with a fingernail.)</t>
+  </si>
+  <si>
+    <t>An old iron door stands ajar, with a conspicuous flat stone wedged in its hinge.</t>
+  </si>
+  <si>
+    <t>The stone I just placed is still wedged in the hinge… best not touch it now.</t>
+  </si>
+  <si>
+    <t>If I knock the stone loose and the door swings shut… I really won’t be able to get out.</t>
+  </si>
+  <si>
+    <t>An iron notice board with worn corners but looking very sturdy; up close there’s a smell of disinfectant</t>
+  </si>
+  <si>
+    <t>As expected, the sky doesn’t drop a windfall twice.</t>
+  </si>
+  <si>
+    <t>Right—this is… environmental cleanup!</t>
+  </si>
+  <si>
+    <t>I almost ran into the Academic Affairs Director on the fifth floor just now—just my luck.</t>
+  </si>
+  <si>
+    <t>The herbicide’s bottle is cold to the touch, and the opening gives off an especially acrid chemical odor</t>
+  </si>
+  <si>
+    <t>The layout is pretty simple: floors one through four are classrooms; the fifth floor is the teachers’ offices, and the Administrative Director’s office is there too...</t>
+  </si>
+  <si>
+    <t>一个不起眼的下水道口，周围湿漉漉的</t>
+  </si>
+  <si>
+    <t>你将&lt;color=#FFC600&gt; [一枚肮脏的硬币] &lt;/color&gt;放入了背包</t>
+  </si>
+  <si>
+    <t>并排放着的三盆植物，最左侧一盆的叶片呈现出健康的翠绿色，中间与右侧盆栽的叶片则显得薄而发黄</t>
+  </si>
+  <si>
+    <t>中间和右边这两盆……叶子又薄又黄，凑近还能闻到一股潮湿霉味和化学药剂的味道</t>
+  </si>
+  <si>
+    <t>它们的黄叶和这股味道肯定有关系</t>
+  </si>
+  <si>
+    <t>这也太惨了，明明并排放着，就最左边那盆幸免于难……</t>
+  </si>
+  <si>
+    <t>You put &lt;color=#FFC600&gt;[a dirty coin]&lt;/color&gt; into your bag.</t>
+  </si>
+  <si>
+    <t>Three potted plants sit side by side; the leftmost has healthy emerald-green leaves, while the leaves of the middle and right pots look thin and yellow.</t>
+  </si>
+  <si>
+    <t>The middle and right pots… their leaves are both thin and yellow, and up close you can smell a damp mustiness mixed with chemicals.</t>
+  </si>
+  <si>
+    <t>The yellowing leaves are definitely connected to that smell.</t>
+  </si>
+  <si>
+    <t>What a pity—set side by side, yet only the leftmost pot was spared…</t>
+  </si>
+  <si>
+    <t>散发着一股恶心的潮湿霉味，总觉得在哪里闻过</t>
+  </si>
+  <si>
+    <t>It gives off a nauseating, damp, moldy smell—I feel like I’ve smelled it somewhere before.</t>
   </si>
 </sst>
 </file>
@@ -882,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B90"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="64.44140625" customWidth="1"/>
@@ -950,7 +1118,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -958,7 +1126,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -966,7 +1134,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -974,15 +1142,15 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -990,31 +1158,31 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1099,514 +1267,738 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>223</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>196</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B65" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B67" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="B72" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73" t="s">
         <v>139</v>
-      </c>
-      <c r="B73" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74" t="s">
         <v>140</v>
-      </c>
-      <c r="B74" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="B76" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="B87" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="B89" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>135</v>
+      </c>
+      <c r="B90" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>154</v>
+      </c>
+      <c r="B91" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>234</v>
+      </c>
+      <c r="B92" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>155</v>
+      </c>
+      <c r="B93" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>156</v>
+      </c>
+      <c r="B94" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>157</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B95" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>158</v>
+      </c>
+      <c r="B96" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>159</v>
+      </c>
+      <c r="B97" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>160</v>
+      </c>
+      <c r="B98" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>161</v>
+      </c>
+      <c r="B99" t="s">
         <v>179</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>163</v>
+      </c>
+      <c r="B101" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>164</v>
+      </c>
+      <c r="B102" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>165</v>
+      </c>
+      <c r="B103" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>166</v>
+      </c>
+      <c r="B104" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>167</v>
+      </c>
+      <c r="B105" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>168</v>
+      </c>
+      <c r="B106" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>169</v>
+      </c>
+      <c r="B107" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>170</v>
+      </c>
+      <c r="B108" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>171</v>
+      </c>
+      <c r="B109" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>172</v>
+      </c>
+      <c r="B110" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>191</v>
+      </c>
+      <c r="B111" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>192</v>
+      </c>
+      <c r="B112" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>193</v>
+      </c>
+      <c r="B113" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>224</v>
+      </c>
+      <c r="B114" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>225</v>
+      </c>
+      <c r="B115" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>226</v>
+      </c>
+      <c r="B116" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>227</v>
+      </c>
+      <c r="B117" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>228</v>
+      </c>
+      <c r="B118" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CDFAD3-A0F9-4671-BC0F-BAE84622F49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6095783-F591-4011-B10E-243FBE78B7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3456" yWindow="4836" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-348" yWindow="5724" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6095783-F591-4011-B10E-243FBE78B7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8915ED0-5E37-4819-B621-564FED490DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-348" yWindow="5724" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7872" yWindow="1716" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="405">
   <si>
     <t>zh</t>
   </si>
@@ -51,9 +51,6 @@
     <t>这地方，除了保洁阿姨固定来打扫，或者外校人来参观的时候，平时根本没人</t>
   </si>
   <si>
-    <t>done!</t>
-  </si>
-  <si>
     <t>I just picked up a flat stone in the corner; it fits perfectly under the hinge of the iron door.</t>
   </si>
   <si>
@@ -315,9 +312,6 @@
     <t>……看来想喝到水，得先在天台上凑够三枚硬币才行</t>
   </si>
   <si>
-    <t>总觉得……刚才好像错过了什么地方，再回去确认一下吧</t>
-  </si>
-  <si>
     <t>一个繁茂的花圃，以鲜黄色花朵为主</t>
   </si>
   <si>
@@ -345,9 +339,6 @@
     <t>The chilled liquid slides down my throat, and that burning restlessness is finally subdued.</t>
   </si>
   <si>
-    <t>I lean against the vending machine and let out a long breath.</t>
-  </si>
-  <si>
     <t>For a moment, the world seems to hit mute; only the slowing rhythm of my heartbeat remains.</t>
   </si>
   <si>
@@ -372,9 +363,6 @@
     <t>…Looks like I’ll need to gather three coins on the rooftop if I want a drink.</t>
   </si>
   <si>
-    <t>I can’t shake the feeling I missed something—better go back and check.</t>
-  </si>
-  <si>
     <t>一个边角有些磨坏但看起来十分结实的铁制公告栏，靠近有消毒水的气味</t>
   </si>
   <si>
@@ -435,60 +423,12 @@
     <t>说是草甸，结果土壤里全是化学药剂的味道和霉味</t>
   </si>
   <si>
-    <t>A bench that appears untended, with moss growing on its legs and on the surrounding ground</t>
-  </si>
-  <si>
-    <t>A tightly shut old iron door; the lock looks very secure</t>
-  </si>
-  <si>
-    <t>A lush flowerbed dominated by bright yellow blossoms</t>
-  </si>
-  <si>
     <t>The writing on it is veiled by a light moss, but still legible:</t>
   </si>
   <si>
-    <t>For safety, please do not lean on or climb the guardrail</t>
-  </si>
-  <si>
-    <t>A cleaning mop with still-damp streaks on it, and next to it a half-full bottle of herbicide</t>
-  </si>
-  <si>
-    <t>From this wet mop you can tell the cleaning lady definitely came by to clean this morning</t>
-  </si>
-  <si>
-    <t>She really went heavy on the stuff—never mind the disinfecting effect, the potency is plenty</t>
-  </si>
-  <si>
-    <t>Bits of gravel everywhere</t>
-  </si>
-  <si>
-    <t>A faint glimmer flickers beneath the gravel</t>
-  </si>
-  <si>
-    <t>You reach out to clear the gravel and, after searching, pick up a silver coin from the soil</t>
-  </si>
-  <si>
-    <t>You search through the gravel again, but find nothing new</t>
-  </si>
-  <si>
-    <t>You find nothing</t>
-  </si>
-  <si>
-    <t>A naturally formed meadow, with all kinds of unknown grasses growing unchecked together</t>
-  </si>
-  <si>
-    <t>The air is a mix of the chemical smell of disinfectant, the musty staleness from the wet mop, and the scent of the earth itself</t>
-  </si>
-  <si>
-    <t>On closer look, many plants show an unnatural wilted state</t>
-  </si>
-  <si>
     <t>Is this some kind of ecological disaster scene?</t>
   </si>
   <si>
-    <t>Call it a meadow, yet the soil reeks of chemicals and mildew</t>
-  </si>
-  <si>
     <t>哇？这个告示牌……</t>
   </si>
   <si>
@@ -549,57 +489,18 @@
     <t>The moss on it is greatly reduced, and there are still marks where it was forcibly rubbed off...</t>
   </si>
   <si>
-    <t>Although I might be overthinking it, this awful feeling is really uncomfortable</t>
-  </si>
-  <si>
     <t>I really hope this is just my imagination...</t>
   </si>
   <si>
-    <t>Since I’m up here, I should carefully check all the places I’m concerned about</t>
-  </si>
-  <si>
     <t>The notice board is checked... what should I examine next again?</t>
   </si>
   <si>
-    <t>In the game, you need to advance the story by completing the items in the &lt;color=#FFC600&gt;Journal&lt;/color&gt;</t>
-  </si>
-  <si>
     <t>In the journal interface, you can distinguish task status by the &lt;color=#FFC600&gt;color&lt;/color&gt; of the entries:</t>
   </si>
   <si>
-    <t>&lt;color=#FFC600&gt;Gray&lt;/color&gt; represents not completed</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFC600&gt;White&lt;/color&gt; represents completed</t>
-  </si>
-  <si>
-    <t>When you clear all the &lt;color=#FFC600&gt;gray&lt;/color&gt; entries in the current journal, a key plot will be triggered</t>
-  </si>
-  <si>
-    <t>Now please press the &lt;color=#FFC600&gt;ESC&lt;/color&gt; key to open the system main menu and check the journal</t>
-  </si>
-  <si>
     <t>Next, go explore the rooftop properly!</t>
   </si>
   <si>
-    <t>The places that need attention should be recorded in the journal</t>
-  </si>
-  <si>
-    <t>I remember the journal mentioned a few key points: the meadow on the left, the potted plants on the right, and the combination of cleaning tools and herbicide</t>
-  </si>
-  <si>
-    <t>Finally gathered three coins</t>
-  </si>
-  <si>
-    <t>Now go take a look at the vending machine</t>
-  </si>
-  <si>
-    <t>I should be able to buy mineral water now</t>
-  </si>
-  <si>
-    <t>Focus on these places; maybe I can figure out what that awful feeling inside is</t>
-  </si>
-  <si>
     <t>一扇虚掩着的老旧铁门，门轴上卡着一块显眼的扁石头</t>
   </si>
   <si>
@@ -678,9 +579,6 @@
     <t>If I knock the stone loose and the door swings shut… I really won’t be able to get out.</t>
   </si>
   <si>
-    <t>An iron notice board with worn corners but looking very sturdy; up close there’s a smell of disinfectant</t>
-  </si>
-  <si>
     <t>As expected, the sky doesn’t drop a windfall twice.</t>
   </si>
   <si>
@@ -690,9 +588,6 @@
     <t>I almost ran into the Academic Affairs Director on the fifth floor just now—just my luck.</t>
   </si>
   <si>
-    <t>The herbicide’s bottle is cold to the touch, and the opening gives off an especially acrid chemical odor</t>
-  </si>
-  <si>
     <t>The layout is pretty simple: floors one through four are classrooms; the fifth floor is the teachers’ offices, and the Administrative Director’s office is there too...</t>
   </si>
   <si>
@@ -733,6 +628,618 @@
   </si>
   <si>
     <t>It gives off a nauseating, damp, moldy smell—I feel like I’ve smelled it somewhere before.</t>
+  </si>
+  <si>
+    <t>刚才把天台上在意的地方都看了一遍</t>
+  </si>
+  <si>
+    <t>那发霉的湿拖把、告示牌上少了一大片的青苔，空气里还有这么浓的除草剂味道</t>
+  </si>
+  <si>
+    <t>难怪总觉得不对劲</t>
+  </si>
+  <si>
+    <t>——这下全都解释得通了</t>
+  </si>
+  <si>
+    <t>哪有什么灵异事件，分明是阿姨早上来除过草了</t>
+  </si>
+  <si>
+    <t>我简直能想象出那个画面</t>
+  </si>
+  <si>
+    <t>阿姨直接把除草剂倒在那根发霉的旧拖把上，把它当大刷子用</t>
+  </si>
+  <si>
+    <t>然后就左一下右一下地，对着长满青苔的墙面和地面使劲刷刮</t>
+  </si>
+  <si>
+    <t>不过被她这么一清理，我倒想起来了——</t>
+  </si>
+  <si>
+    <t>刚才在草甸旁边走的时候，就觉得那片土特别眼熟</t>
+  </si>
+  <si>
+    <t>哈哈，一不小心就让我想起来了</t>
+  </si>
+  <si>
+    <t>上上周的周三，我趁体育课自由活动的时间溜上来过</t>
+  </si>
+  <si>
+    <t>那天早上路过校门口的花店，老板正把过季的铃兰种球往垃圾袋里倒，圆溜溜的种球滚了一地</t>
+  </si>
+  <si>
+    <t>我这手欠的，实在是没忍住，就捡了一颗最饱满的</t>
+  </si>
+  <si>
+    <t>听店员在旁边嘀咕，说这些种球存放太久，都失去活性了</t>
+  </si>
+  <si>
+    <t>他越是这么说，我越是想试试</t>
+  </si>
+  <si>
+    <t>说实在的，我对养花种草完全不懂，完全是瞎猫碰上死耗子，胡乱往草甸里一埋</t>
+  </si>
+  <si>
+    <t>想着这么多天过去，说不定真有奇迹发生呢……</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>……</t>
+  </si>
+  <si>
+    <t>…………</t>
+  </si>
+  <si>
+    <t>等等</t>
+  </si>
+  <si>
+    <t>阿姨今天清除了青苔，肯定也除了草甸里的杂草…</t>
+  </si>
+  <si>
+    <t>？那我的种球！</t>
+  </si>
+  <si>
+    <t>记得当时埋得挺隐蔽的，但要是阿姨认真起来……</t>
+  </si>
+  <si>
+    <t>不行，我得赶快去&lt;color=#FFC600&gt;草甸&lt;/color&gt;的地方确认一下</t>
+  </si>
+  <si>
+    <t>到了到了，就是这里！</t>
+  </si>
+  <si>
+    <t>……这里除草剂的味道也太冲了，呛得人喘不过气</t>
+  </si>
+  <si>
+    <t>我得赶紧把土翻开看看，要是种球状态不好就马上移栽到别的地方</t>
+  </si>
+  <si>
+    <t>……等等</t>
+  </si>
+  <si>
+    <t>我上上周把它埋在哪里来着</t>
+  </si>
+  <si>
+    <t>……完了，完全想不起来了</t>
+  </si>
+  <si>
+    <t>这得找到什么时候去啊，只能硬着头皮一块一块翻了</t>
+  </si>
+  <si>
+    <t>！找到了</t>
+  </si>
+  <si>
+    <t>就是这块土，草皮比旁边薄了很多</t>
+  </si>
+  <si>
+    <t>……我完全记起来了</t>
+  </si>
+  <si>
+    <t>上次来的时候顺手把这里的草拔掉了，才空出地方来种我的种球的</t>
+  </si>
+  <si>
+    <t>（我俯下身来，确认铃兰种球的状态）</t>
+  </si>
+  <si>
+    <t>视线落回那方泥土，我的呼吸不由得一滞</t>
+  </si>
+  <si>
+    <t>它居然……破土了</t>
+  </si>
+  <si>
+    <t>那两片细细的披针叶，薄如蝉翼</t>
+  </si>
+  <si>
+    <t>在斜照过来的光线下，呈现出一种半透明的质感</t>
+  </si>
+  <si>
+    <t>叶脉如同最精细的工笔画，清晰地在其中延展</t>
+  </si>
+  <si>
+    <t>它们通透得仿佛能过滤尘世的喧嚣，将周围所有的嘈杂都净化成一种寂静的喜悦</t>
+  </si>
+  <si>
+    <t>我不禁感叹</t>
+  </si>
+  <si>
+    <t>生命真是神奇</t>
+  </si>
+  <si>
+    <t>这孱弱的新绿，竟能在土壤里找到出路</t>
+  </si>
+  <si>
+    <t>只是遵循着最原始的本能，安静地完成破土的仪式</t>
+  </si>
+  <si>
+    <t>我也就在这一刻，忽然明白</t>
+  </si>
+  <si>
+    <t>我见证的不只是一株植物的破土</t>
+  </si>
+  <si>
+    <t>更是一个微小而确凿的奇迹</t>
+  </si>
+  <si>
+    <t>…………？</t>
+  </si>
+  <si>
+    <t>……………………？？</t>
+  </si>
+  <si>
+    <t>…………………………………………？？？</t>
+  </si>
+  <si>
+    <t>……………………………………………………………………………………？？？？</t>
+  </si>
+  <si>
+    <t>我去！我把跑操忘得一干二净</t>
+  </si>
+  <si>
+    <t>而且这周还是班主任亲自查勤</t>
+  </si>
+  <si>
+    <t>就因为上周领导视察，队伍出发时倒是整整齐齐</t>
+  </si>
+  <si>
+    <t>有人跑到一半鞋带就恰到好处地散了，蹲下去就再没跟上来</t>
+  </si>
+  <si>
+    <t>还有几个在领导眼皮子底下递眼神，趁着拐弯，一个接一个猫着腰闪进了教学楼楼梯间</t>
+  </si>
+  <si>
+    <t>跑一圈回来队伍的人数直接少了一半</t>
+  </si>
+  <si>
+    <t>气得领导训话了一个小时……接下来一个月严抓纪律</t>
+  </si>
+  <si>
+    <t>要是全班都站得整整齐齐，就我的位置空着</t>
+  </si>
+  <si>
+    <t>……这不是纯纯往枪口上撞吗</t>
+  </si>
+  <si>
+    <t>……班主任那边可不是好糊弄的</t>
+  </si>
+  <si>
+    <t>我得赶紧下去，现在过去说不定还能混进队伍里</t>
+  </si>
+  <si>
+    <t>小陈啊，我今天上来看看天台的定期维修情况，上周你报修的防护栏应该被修好了</t>
+  </si>
+  <si>
+    <t>虽然平时没有人来，但是有些安全隐患还是要定期检查</t>
+  </si>
+  <si>
+    <t>上周来的工人除了修理护栏，他还反馈天台上的金属被青苔锈蚀严重，需要定期清理</t>
+  </si>
+  <si>
+    <t>让主任您费心了，还专门跑一趟</t>
+  </si>
+  <si>
+    <t>护栏已经修好了，至于青苔，还是您考虑得周到，一直惦记着这事</t>
+  </si>
+  <si>
+    <t>请您放心，今天一早我特意安排了李阿姨上来，都清理干净了</t>
+  </si>
+  <si>
+    <t>……我去，是刚刚楼梯口遇见的教导主任，他已经在开门了</t>
+  </si>
+  <si>
+    <t>***，麻绳专挑细处断，噩运只找苦命人</t>
+  </si>
+  <si>
+    <t>快跑啊</t>
+  </si>
+  <si>
+    <t>我急匆匆地打开门，正要一步跨下楼梯</t>
+  </si>
+  <si>
+    <t>就在我以为只要跑得够快就能逃过一劫的瞬间</t>
+  </si>
+  <si>
+    <t>可就在抬脚发力、身体前倾的瞬间——一阵剧痛和冰冷的禁锢感向我袭来</t>
+  </si>
+  <si>
+    <t>那块我上来时随手卡住铁门的扁石头</t>
+  </si>
+  <si>
+    <t>此刻像道冰冷的铁箍，精准地咬住了我的脚踝</t>
+  </si>
+  <si>
+    <t>我整个人如同一截被伐倒的木头</t>
+  </si>
+  <si>
+    <t>完全不受控制地向前、无可挽回地向着陡峭的台阶一路翻滚、撞击着栽了下去</t>
+  </si>
+  <si>
+    <t>当最终摔落在底层地面时，视野瞬间陷入一片漆黑，鲜红色的液体从额际淌下</t>
+  </si>
+  <si>
+    <t>那时我怎么会想到</t>
+  </si>
+  <si>
+    <t>这不过是一切噩梦的开端</t>
+  </si>
+  <si>
+    <t>I just went over all the spots I care about on the rooftop</t>
+  </si>
+  <si>
+    <t>But after she cleaned it up like that, it reminded me—</t>
+  </si>
+  <si>
+    <t>I figured after so many days, maybe a miracle really happened…</t>
+  </si>
+  <si>
+    <t>If she cleared the moss today, she definitely weeded the meadow too…</t>
+  </si>
+  <si>
+    <t>Huh? What about my bulb!</t>
+  </si>
+  <si>
+    <t>I remember burying it pretty well, but if she got serious…</t>
+  </si>
+  <si>
+    <t>Here we are, this is the spot!</t>
+  </si>
+  <si>
+    <t>…The herbicide smell here is way too strong, it’s choking</t>
+  </si>
+  <si>
+    <t>Found it!</t>
+  </si>
+  <si>
+    <t>(I bend down to check the bulb’s condition)</t>
+  </si>
+  <si>
+    <t>It actually… broke through the surface</t>
+  </si>
+  <si>
+    <t>Two slender lanceolate leaves, thin as cicada wings</t>
+  </si>
+  <si>
+    <t>…………?</t>
+  </si>
+  <si>
+    <t>……………………??</t>
+  </si>
+  <si>
+    <t>…………………………………………???</t>
+  </si>
+  <si>
+    <t>……………………………………………………………………………………????</t>
+  </si>
+  <si>
+    <t>Crap!</t>
+  </si>
+  <si>
+    <t>Run!</t>
+  </si>
+  <si>
+    <t>总觉得……刚才好像错过了什么地方，再去&lt;color=#FFC600&gt;日记&lt;/color&gt;里确认一下吧</t>
+  </si>
+  <si>
+    <t>糟了！</t>
+  </si>
+  <si>
+    <t>This was only the beginning of the nightmare.</t>
+  </si>
+  <si>
+    <t>Completely out of control, tumbling helplessly down the steep stairs, slamming into the edges step after step.</t>
+  </si>
+  <si>
+    <t>When I finally hit the ground floor, my vision goes instantly black, and bright red runs from my brow.</t>
+  </si>
+  <si>
+    <t>I pitch forward like a felled log.</t>
+  </si>
+  <si>
+    <t>Now bites my ankle like a cold iron hoop, precisely and cruelly.</t>
+  </si>
+  <si>
+    <t>The flat stone I’d wedged in the iron door when I came up.</t>
+  </si>
+  <si>
+    <t>At the very moment I push off, body leaning forward—a stab of pain and cold restraint clamps down on me.</t>
+  </si>
+  <si>
+    <t>Just when I thought running fast would let me escape.</t>
+  </si>
+  <si>
+    <t>I yank the door open and am about to take the first step down the stairs.</t>
+  </si>
+  <si>
+    <t>D***, the rope always snaps at its thinnest; misfortune picks on the miserable.</t>
+  </si>
+  <si>
+    <t>…Oh no, it’s the Academic Affairs Director I just ran into at the stairwell—he’s already unlocking the door.</t>
+  </si>
+  <si>
+    <t>Please rest assured, I specifically arranged for Auntie Li to come up early this morning; it’s all been cleaned.</t>
+  </si>
+  <si>
+    <t>The guardrail has been repaired, and as for the moss, you were thoughtful to keep it in mind—we’ve been aware of it.</t>
+  </si>
+  <si>
+    <t>Thank you for the trouble, Director, for making a special trip.</t>
+  </si>
+  <si>
+    <t>Besides fixing the guardrail, the worker last week also reported that the rooftop metal was badly corroded by moss and needs routine cleaning.</t>
+  </si>
+  <si>
+    <t>Even though people rarely come up here, we still need to check for safety hazards regularly.</t>
+  </si>
+  <si>
+    <t>Chen, I came up today to check the rooftop’s regular maintenance. The guardrail you reported last week should have been fixed.</t>
+  </si>
+  <si>
+    <t>I’ve got to get downstairs—if I go now, maybe I can still blend into the lineup.</t>
+  </si>
+  <si>
+    <t>…the homeroom teacher isn’t easy to fool.</t>
+  </si>
+  <si>
+    <t>…That’s basically sticking my head in the lion’s mouth.</t>
+  </si>
+  <si>
+    <t>If the whole class is standing in perfect rows with only my spot empty.</t>
+  </si>
+  <si>
+    <t>The leaders were so mad they lectured us for an hour… and discipline will be strict for the next month.</t>
+  </si>
+  <si>
+    <t>By the time we got back, the team had half the people.</t>
+  </si>
+  <si>
+    <t>A few others traded looks right under the leaders’ noses and, at the turn, slipped one by one into the stairwell of the teaching building.</t>
+  </si>
+  <si>
+    <t>But halfway through, someone’s shoelace oh-so-conveniently came undone, they squatted down and never caught up.</t>
+  </si>
+  <si>
+    <t>Because during last week’s leadership inspection, the lineup looked tidy at the start.</t>
+  </si>
+  <si>
+    <t>And this week the homeroom teacher is checking attendance in person.</t>
+  </si>
+  <si>
+    <t>Oh no! I completely forgot about the morning run.</t>
+  </si>
+  <si>
+    <t>It was a tiny yet undeniable miracle.</t>
+  </si>
+  <si>
+    <t>What I witnessed wasn’t just a plant breaking ground.</t>
+  </si>
+  <si>
+    <t>And at that very moment, I suddenly understood.</t>
+  </si>
+  <si>
+    <t>Simply following its oldest instinct, quietly completing the rite of emergence.</t>
+  </si>
+  <si>
+    <t>This fragile new green still found a way through the soil.</t>
+  </si>
+  <si>
+    <t>Life is truly miraculous.</t>
+  </si>
+  <si>
+    <t>They’re so clear it’s as if they filter out the world’s clamor, turning all the noise around into a quiet joy.</t>
+  </si>
+  <si>
+    <t>The veins stretch inside like the finest brushwork.</t>
+  </si>
+  <si>
+    <t>In the slanting light, they show a translucent texture.</t>
+  </si>
+  <si>
+    <t>You find nothing.</t>
+  </si>
+  <si>
+    <t>You search through the gravel again, but find nothing new.</t>
+  </si>
+  <si>
+    <t>You reach out to clear the gravel and, after searching, pick up a silver coin from the soil.</t>
+  </si>
+  <si>
+    <t>A naturally formed meadow, with all kinds of unknown grasses growing unchecked together.</t>
+  </si>
+  <si>
+    <t>The air is a mix of the chemical smell of disinfectant, the musty staleness from the wet mop, and the scent of the earth itself.</t>
+  </si>
+  <si>
+    <t>On closer look, many plants show an unnatural wilted state.</t>
+  </si>
+  <si>
+    <t>Call it a meadow, yet the soil reeks of chemicals and mildew.</t>
+  </si>
+  <si>
+    <t>Although I might be overthinking it, this awful feeling is really uncomfortable.</t>
+  </si>
+  <si>
+    <t>Since I’m up here, I should carefully check all the places I’m concerned about.</t>
+  </si>
+  <si>
+    <t>My gaze falls back onto that bit of soil, and my breath catches.</t>
+  </si>
+  <si>
+    <t>Last time I came, I yanked out the grass here, which made space to plant my bulb.</t>
+  </si>
+  <si>
+    <t>I have a feeling I missed something just now—better check the &lt;color=#FFC600&gt;Journal&lt;/color&gt; again.</t>
+  </si>
+  <si>
+    <t>A bench that appears untended, with moss growing on its legs and on the surrounding ground.</t>
+  </si>
+  <si>
+    <t>A tightly shut old iron door; the lock looks very secure.</t>
+  </si>
+  <si>
+    <t>A lush flowerbed dominated by bright yellow blossoms.</t>
+  </si>
+  <si>
+    <t>An iron notice board with worn corners but looking very sturdy; up close there’s a smell of disinfectant.</t>
+  </si>
+  <si>
+    <t>For safety, please do not lean on or climb the guardrail.</t>
+  </si>
+  <si>
+    <t>A cleaning mop with still-damp streaks on it, and next to it a half-full bottle of herbicide.</t>
+  </si>
+  <si>
+    <t>The herbicide’s bottle is cold to the touch, and the opening gives off an especially acrid chemical odor.</t>
+  </si>
+  <si>
+    <t>From this wet mop you can tell the cleaning lady definitely came by to clean this morning.</t>
+  </si>
+  <si>
+    <t>She really went heavy on the stuff—never mind the disinfecting effect, the potency is plenty.</t>
+  </si>
+  <si>
+    <t>…I remember everything now.</t>
+  </si>
+  <si>
+    <t>It’s this patch; the turf is much thinner than the rest.</t>
+  </si>
+  <si>
+    <t>How long will this take to find—guess I’ll have to grit my teeth and flip the soil chunk by chunk.</t>
+  </si>
+  <si>
+    <t>…Crap, I can’t remember at all.</t>
+  </si>
+  <si>
+    <t>…Wait.</t>
+  </si>
+  <si>
+    <t>Where exactly did I bury it two weeks ago?</t>
+  </si>
+  <si>
+    <t>I need to quickly turn the soil and look—if the bulb isn’t doing well, I’ll transplant it right away.</t>
+  </si>
+  <si>
+    <t>No, I have to hurry and check the &lt;color=#FFC600&gt;meadow&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Wait!</t>
+  </si>
+  <si>
+    <t>Honestly, I know nothing about gardening; it was pure dumb luck—I just shoved it randomly into the meadow.</t>
+  </si>
+  <si>
+    <t>The more he said that, the more I wanted to try.</t>
+  </si>
+  <si>
+    <t>I heard the clerk muttering that the bulbs had been stored too long and had lost their vitality.</t>
+  </si>
+  <si>
+    <t>I couldn’t help myself—my itchy hands picked up the plumpest one.</t>
+  </si>
+  <si>
+    <t>That morning, I passed the flower shop at the school gate; the owner was dumping out-of-season lily-of-the-valley bulbs into a trash bag, and the round bulbs rolled all over the sidewalk.</t>
+  </si>
+  <si>
+    <t>Two Wednesdays ago, I slipped up here during free time in PE class.</t>
+  </si>
+  <si>
+    <t>Haha, and without meaning to, it made me remember.</t>
+  </si>
+  <si>
+    <t>When I walked by the meadow just now, that patch of soil looked really familiar.</t>
+  </si>
+  <si>
+    <t>Then scrubbed hard left and right across the mossy walls and floor.</t>
+  </si>
+  <si>
+    <t>Bits of gravel everywhere.</t>
+  </si>
+  <si>
+    <t>A faint glimmer flickers beneath the gravel.</t>
+  </si>
+  <si>
+    <t>In the game, you need to advance the story by completing the items in the &lt;color=#FFC600&gt;Journal&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFC600&gt;Gray&lt;/color&gt; represents not completed.</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFC600&gt;White&lt;/color&gt; represents completed.</t>
+  </si>
+  <si>
+    <t>When you clear all the &lt;color=#FFC600&gt;gray&lt;/color&gt; entries in the current journal, a key plot will be triggered.</t>
+  </si>
+  <si>
+    <t>Now please press the &lt;color=#FFC600&gt;ESC&lt;/color&gt; key to open the system main menu and check the journal.</t>
+  </si>
+  <si>
+    <t>The places that need attention should be recorded in the journal.</t>
+  </si>
+  <si>
+    <t>I remember the journal mentioned a few key points: the meadow on the left, the potted plants on the right, and the combination of cleaning tools and herbicide.</t>
+  </si>
+  <si>
+    <t>Focus on these places; maybe I can figure out what that awful feeling inside is.</t>
+  </si>
+  <si>
+    <t>She poured the herbicide onto that moldy old mop and used it like a giant brush.</t>
+  </si>
+  <si>
+    <t>I can practically picture it.</t>
+  </si>
+  <si>
+    <t>There was no haunting at all; the auntie clearly came by this morning to weed.</t>
+  </si>
+  <si>
+    <t>No wonder something felt off.</t>
+  </si>
+  <si>
+    <t>That moldy wet mop, the big patch of moss missing from the notice board, and the strong smell of herbicide lingering in the air.</t>
+  </si>
+  <si>
+    <t>Finally gathered three coins.</t>
+  </si>
+  <si>
+    <t>Now go take a look at the vending machine.</t>
+  </si>
+  <si>
+    <t>I should be able to buy mineral water now.</t>
+  </si>
+  <si>
+    <t>Done!</t>
+  </si>
+  <si>
+    <t>I couldn’t have known then.</t>
+  </si>
+  <si>
+    <t>I can’t help but marvel.</t>
+  </si>
+  <si>
+    <t>I lean against the vending machine and let out a long, deep breath.</t>
+  </si>
+  <si>
+    <t>—Now everything makes sense.</t>
   </si>
 </sst>
 </file>
@@ -1050,11 +1557,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="64.44140625" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="2" max="2" width="117" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -1070,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1078,7 +1585,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1086,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1094,7 +1601,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1102,7 +1609,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1110,895 +1617,1623 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="B27" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s">
         <v>50</v>
-      </c>
-      <c r="B37" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>403</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>304</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>354</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>355</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>356</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>357</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>217</v>
+        <v>358</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B73" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>221</v>
+        <v>361</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B77" t="s">
-        <v>142</v>
+        <v>362</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B78" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B79" t="s">
-        <v>143</v>
+        <v>363</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>382</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B85" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B87" t="s">
-        <v>150</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B88" t="s">
-        <v>151</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B90" t="s">
-        <v>153</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B91" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="B92" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B93" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B94" t="s">
-        <v>174</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B95" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B96" t="s">
-        <v>176</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B98" t="s">
-        <v>178</v>
+        <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B99" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B100" t="s">
-        <v>180</v>
+        <v>385</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B101" t="s">
-        <v>181</v>
+        <v>386</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B102" t="s">
-        <v>182</v>
+        <v>387</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B103" t="s">
-        <v>183</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B104" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B105" t="s">
-        <v>185</v>
+        <v>389</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>390</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="B107" t="s">
-        <v>190</v>
+        <v>391</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B108" t="s">
-        <v>187</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="B109" t="s">
-        <v>188</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B110" t="s">
-        <v>189</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="B111" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="B112" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="B113" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B114" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B115" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="B116" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="B117" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>193</v>
+      </c>
+      <c r="B118" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>201</v>
+      </c>
+      <c r="B119" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>202</v>
+      </c>
+      <c r="B120" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>203</v>
+      </c>
+      <c r="B121" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>204</v>
+      </c>
+      <c r="B122" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>205</v>
+      </c>
+      <c r="B123" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>206</v>
+      </c>
+      <c r="B124" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>207</v>
+      </c>
+      <c r="B125" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>208</v>
+      </c>
+      <c r="B126" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>209</v>
+      </c>
+      <c r="B127" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>210</v>
+      </c>
+      <c r="B128" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>211</v>
+      </c>
+      <c r="B129" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>212</v>
+      </c>
+      <c r="B130" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>213</v>
+      </c>
+      <c r="B131" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>214</v>
+      </c>
+      <c r="B132" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>215</v>
+      </c>
+      <c r="B133" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>216</v>
+      </c>
+      <c r="B134" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>217</v>
+      </c>
+      <c r="B135" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>218</v>
+      </c>
+      <c r="B136" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>219</v>
+      </c>
+      <c r="B137" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>220</v>
+      </c>
+      <c r="B138" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>221</v>
+      </c>
+      <c r="B139" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>222</v>
+      </c>
+      <c r="B140" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>223</v>
+      </c>
+      <c r="B141" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>224</v>
+      </c>
+      <c r="B142" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>225</v>
+      </c>
+      <c r="B143" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>226</v>
+      </c>
+      <c r="B144" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>227</v>
+      </c>
+      <c r="B145" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>228</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B146" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>229</v>
+      </c>
+      <c r="B147" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>220</v>
+      </c>
+      <c r="B148" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>230</v>
+      </c>
+      <c r="B149" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>231</v>
+      </c>
+      <c r="B150" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>232</v>
+      </c>
+      <c r="B151" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>233</v>
+      </c>
+      <c r="B152" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>234</v>
+      </c>
+      <c r="B153" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>235</v>
+      </c>
+      <c r="B154" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>236</v>
+      </c>
+      <c r="B155" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>237</v>
+      </c>
+      <c r="B156" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>238</v>
+      </c>
+      <c r="B157" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>239</v>
+      </c>
+      <c r="B158" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>240</v>
+      </c>
+      <c r="B159" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>241</v>
+      </c>
+      <c r="B160" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>242</v>
+      </c>
+      <c r="B161" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>243</v>
+      </c>
+      <c r="B162" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>244</v>
+      </c>
+      <c r="B163" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>245</v>
+      </c>
+      <c r="B164" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>246</v>
+      </c>
+      <c r="B165" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>247</v>
+      </c>
+      <c r="B166" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>248</v>
+      </c>
+      <c r="B167" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>249</v>
+      </c>
+      <c r="B168" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>250</v>
+      </c>
+      <c r="B169" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>251</v>
+      </c>
+      <c r="B170" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>219</v>
+      </c>
+      <c r="B171" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>220</v>
+      </c>
+      <c r="B172" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>252</v>
+      </c>
+      <c r="B173" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>253</v>
+      </c>
+      <c r="B174" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>254</v>
+      </c>
+      <c r="B175" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>255</v>
+      </c>
+      <c r="B176" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>256</v>
+      </c>
+      <c r="B177" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>257</v>
+      </c>
+      <c r="B178" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>258</v>
+      </c>
+      <c r="B179" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>259</v>
+      </c>
+      <c r="B180" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>260</v>
+      </c>
+      <c r="B181" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>261</v>
+      </c>
+      <c r="B182" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>262</v>
+      </c>
+      <c r="B183" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>263</v>
+      </c>
+      <c r="B184" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>264</v>
+      </c>
+      <c r="B185" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>265</v>
+      </c>
+      <c r="B186" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>266</v>
+      </c>
+      <c r="B187" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>267</v>
+      </c>
+      <c r="B188" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>268</v>
+      </c>
+      <c r="B189" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>269</v>
+      </c>
+      <c r="B190" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>270</v>
+      </c>
+      <c r="B191" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>271</v>
+      </c>
+      <c r="B192" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>272</v>
+      </c>
+      <c r="B193" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>273</v>
+      </c>
+      <c r="B194" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>274</v>
+      </c>
+      <c r="B195" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>275</v>
+      </c>
+      <c r="B196" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>276</v>
+      </c>
+      <c r="B197" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>277</v>
+      </c>
+      <c r="B198" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>278</v>
+      </c>
+      <c r="B199" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>279</v>
+      </c>
+      <c r="B200" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>280</v>
+      </c>
+      <c r="B201" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>305</v>
+      </c>
+      <c r="B202" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>281</v>
+      </c>
+      <c r="B203" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>282</v>
+      </c>
+      <c r="B204" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>283</v>
+      </c>
+      <c r="B205" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>220</v>
+      </c>
+      <c r="B206" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>221</v>
+      </c>
+      <c r="B207" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>284</v>
+      </c>
+      <c r="B208" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>285</v>
+      </c>
+      <c r="B209" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8915ED0-5E37-4819-B621-564FED490DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AAFFB0C-7146-4502-85B9-DC89B5AF38FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7872" yWindow="1716" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="2928" windowWidth="16272" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AAFFB0C-7146-4502-85B9-DC89B5AF38FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED39FEFD-208C-414B-A4F4-3B43AD5EB586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="2928" windowWidth="16272" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2688" windowWidth="23040" windowHeight="6144" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,12 +90,6 @@
     <t>顺着地上的脚印移动到身后的告示牌上吧</t>
   </si>
   <si>
-    <t>You can now move the character with WASD and the arrow keys.</t>
-  </si>
-  <si>
-    <t>While moving, press Right Shift to move faster.</t>
-  </si>
-  <si>
     <t>Follow the footprints on the ground to the notice board behind you.</t>
   </si>
   <si>
@@ -1240,6 +1234,12 @@
   </si>
   <si>
     <t>—Now everything makes sense.</t>
+  </si>
+  <si>
+    <t>While moving, press &lt;color=#FFC600&gt;Left Shift&lt;/color&gt; to move faster.</t>
+  </si>
+  <si>
+    <t>Now you can press &lt;color=#FFC600&gt;WASD&lt;/color&gt; and the &lt;color=#FFC600&gt;arrow keys&lt;/color&gt; to move your character.</t>
   </si>
 </sst>
 </file>
@@ -1577,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1633,7 +1633,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1641,7 +1641,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1649,15 +1649,15 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1665,31 +1665,31 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1697,7 +1697,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1705,7 +1705,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1713,1527 +1713,1527 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B63" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B69" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B70" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B71" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B72" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B74" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B75" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B76" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B77" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B79" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B80" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B81" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B82" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B83" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B84" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B86" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B87" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B88" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B89" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B90" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B91" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B93" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B94" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B96" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B97" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B98" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B99" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B101" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B102" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B103" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B104" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B105" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B106" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B107" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B108" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B109" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B110" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B111" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B112" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B113" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B114" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B115" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B116" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B117" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B118" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B119" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B120" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B121" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B122" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B123" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B124" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B125" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B126" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B127" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B128" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B129" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B130" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B131" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B132" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B133" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B134" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B135" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B136" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B137" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B138" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B139" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B140" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B141" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B142" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B143" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B144" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B145" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B146" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B147" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B148" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B149" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B150" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B151" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B152" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B153" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B154" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B155" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B156" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B157" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B158" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B159" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B160" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B161" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B162" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B163" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B164" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B165" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B166" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B167" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B168" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B169" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B170" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B171" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B172" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B173" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B174" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B175" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B176" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B177" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B178" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B179" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B180" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B181" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B182" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B183" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B184" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B185" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B186" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B187" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B188" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B189" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B190" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B191" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B192" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B193" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B194" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B195" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B196" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B197" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B198" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B199" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B200" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B201" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B202" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B203" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B204" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B205" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B206" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B207" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B208" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B209" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED39FEFD-208C-414B-A4F4-3B43AD5EB586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621CAFC-EF1A-4FEB-A0A6-6DEA36E689A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2688" windowWidth="23040" windowHeight="6144" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="407">
   <si>
     <t>zh</t>
   </si>
@@ -87,12 +87,6 @@
     <t>在移动的过程中按下右Shift键可以快速移动</t>
   </si>
   <si>
-    <t>顺着地上的脚印移动到身后的告示牌上吧</t>
-  </si>
-  <si>
-    <t>Follow the footprints on the ground to the notice board behind you.</t>
-  </si>
-  <si>
     <t>靠近可交互的物体时，人物上方将显示交互图标</t>
   </si>
   <si>
@@ -1240,6 +1234,18 @@
   </si>
   <si>
     <t>Now you can press &lt;color=#FFC600&gt;WASD&lt;/color&gt; and the &lt;color=#FFC600&gt;arrow keys&lt;/color&gt; to move your character.</t>
+  </si>
+  <si>
+    <t>顺着地上的脚印移动到身后的&lt;color=#FFC600&gt;告示牌&lt;/color&gt;上吧</t>
+  </si>
+  <si>
+    <t>Follow the footprints on the ground to the &lt;color=#FFC600&gt;notice board&lt;/color&gt; behind you.</t>
+  </si>
+  <si>
+    <t>请按下&lt;color=#FFC600&gt;ESC&lt;/color&gt;键，打开系统的主菜单查阅日记</t>
+  </si>
+  <si>
+    <t>Press the &lt;color=#FFC600&gt;ESC&lt;/color&gt; key to open the system main menu and check the journal.</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B209"/>
+  <dimension ref="A1:B210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="64.44140625" customWidth="1"/>
@@ -1577,7 +1583,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1625,7 +1631,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1633,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1641,7 +1647,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1649,15 +1655,15 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1665,31 +1671,31 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1697,7 +1703,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1705,1068 +1711,1068 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>403</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B36" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B61" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B68" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B69" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B72" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B74" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B75" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B76" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B77" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B79" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B80" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B81" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B82" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B83" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B84" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B86" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B87" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B88" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B89" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B90" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B91" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B93" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B94" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B95" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B96" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B97" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B98" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B99" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B100" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B101" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B102" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B103" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>144</v>
+        <v>405</v>
       </c>
       <c r="B104" t="s">
-        <v>155</v>
+        <v>406</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B105" t="s">
-        <v>387</v>
+        <v>153</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B106" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B107" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B108" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B109" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B110" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B111" t="s">
-        <v>179</v>
+        <v>395</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B112" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B113" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="B114" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B116" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B117" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B118" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B119" t="s">
-        <v>284</v>
+        <v>194</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B120" t="s">
-        <v>394</v>
+        <v>282</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B121" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B122" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B123" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B124" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B125" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B126" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B127" t="s">
-        <v>285</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B128" t="s">
-        <v>378</v>
+        <v>283</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B129" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B130" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B131" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B132" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B133" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B134" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B135" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B136" t="s">
-        <v>286</v>
+        <v>369</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B137" t="s">
-        <v>217</v>
+        <v>284</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B138" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B139" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B140" t="s">
-        <v>370</v>
+        <v>217</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B141" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B142" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B143" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B144" t="s">
-        <v>369</v>
+        <v>287</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B145" t="s">
-        <v>290</v>
+        <v>367</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B146" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B147" t="s">
-        <v>368</v>
+        <v>289</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B148" t="s">
-        <v>217</v>
+        <v>366</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B149" t="s">
-        <v>366</v>
+        <v>215</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B150" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B151" t="s">
         <v>365</v>
@@ -2774,423 +2780,423 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B152" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B153" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B154" t="s">
-        <v>363</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B155" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B156" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B157" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B158" t="s">
-        <v>350</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B159" t="s">
-        <v>294</v>
+        <v>348</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B160" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B161" t="s">
-        <v>340</v>
+        <v>293</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B162" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B163" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B164" t="s">
-        <v>400</v>
+        <v>336</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B165" t="s">
-        <v>337</v>
+        <v>398</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B166" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B167" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B168" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B169" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B170" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="B171" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B172" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="B173" t="s">
-        <v>296</v>
+        <v>216</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B174" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B175" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B176" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B177" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B178" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B179" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B180" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B181" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B182" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B183" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B184" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B185" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B186" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B187" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B188" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B189" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B190" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B191" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B192" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B193" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B194" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B195" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B196" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B197" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B198" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B199" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B200" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B201" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="B202" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="B203" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B204" t="s">
         <v>305</v>
@@ -3198,42 +3204,50 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B205" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="B206" t="s">
-        <v>217</v>
+        <v>304</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B207" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>282</v>
+        <v>217</v>
       </c>
       <c r="B208" t="s">
-        <v>399</v>
+        <v>216</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B209" t="s">
-        <v>304</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>281</v>
+      </c>
+      <c r="B210" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-Main/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621CAFC-EF1A-4FEB-A0A6-6DEA36E689A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422F6C63-D317-422C-8259-989C30FAF747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2688" windowWidth="23040" windowHeight="6144" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -81,12 +81,6 @@
     <t>上次来……是上周？还是上上周？具体时间完全想不起来了</t>
   </si>
   <si>
-    <t>现在你可以按下WASD和方向键来移动人物</t>
-  </si>
-  <si>
-    <t>在移动的过程中按下右Shift键可以快速移动</t>
-  </si>
-  <si>
     <t>靠近可交互的物体时，人物上方将显示交互图标</t>
   </si>
   <si>
@@ -1246,6 +1240,12 @@
   </si>
   <si>
     <t>Press the &lt;color=#FFC600&gt;ESC&lt;/color&gt; key to open the system main menu and check the journal.</t>
+  </si>
+  <si>
+    <t>现在你可以按下&lt;color=#FFC600&gt;WASD&lt;/color&gt;和&lt;color=#FFC600&gt;方向键&lt;/color&gt;来移动人物</t>
+  </si>
+  <si>
+    <t>在移动的过程中按下&lt;color=#FFC600&gt;左Shift键&lt;/color&gt;可以快速移动</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1583,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1631,7 +1631,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1639,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1647,7 +1647,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1655,15 +1655,15 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1671,1583 +1671,1583 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="B17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>406</v>
       </c>
       <c r="B18" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B19" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B68" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B70" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B71" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B72" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B74" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B75" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B79" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B80" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B81" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B82" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B83" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B84" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B86" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B87" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B88" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B89" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B90" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B91" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B93" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B94" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B95" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B97" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B101" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B102" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B103" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B104" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B106" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B107" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B108" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B109" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B110" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B111" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B112" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B113" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B114" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B115" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B116" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B117" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B118" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B119" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B120" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B121" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B122" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B123" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B124" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B125" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B126" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B127" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B128" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B129" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B130" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B131" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B132" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B133" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B134" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B135" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B136" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B137" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B138" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B139" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B140" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B141" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B142" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B143" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B144" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B145" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B147" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B148" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B149" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B150" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B151" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B152" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B153" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B154" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B155" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B156" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B157" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B158" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B159" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B160" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B161" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B162" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B163" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B164" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B165" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B166" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B167" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B168" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B169" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B170" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B171" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B172" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B173" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B174" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B175" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B176" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B177" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B178" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B179" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B180" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B181" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B182" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B183" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B184" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B185" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B186" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B187" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B188" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B189" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B190" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B191" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B192" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B193" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B194" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B195" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B196" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B197" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B198" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B199" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B200" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B201" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B202" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B203" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B204" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B205" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B206" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B207" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B208" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B209" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B210" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
